--- a/data/trans_orig/IMC_inf_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20987</t>
+          <t>20798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10376</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13930</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26105</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37408</t>
+          <t>38369</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45167</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58935</t>
+          <t>58319</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26198</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>39030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74596</t>
+          <t>74502</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95104</t>
+          <t>94896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6398</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28833</t>
+          <t>28349</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>28171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48008</t>
+          <t>46927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46023</t>
+          <t>46526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68968</t>
+          <t>70926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41662</t>
+          <t>41866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30110</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49126</t>
+          <t>48887</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57690</t>
+          <t>58410</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84087</t>
+          <t>84085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62212</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86607</t>
+          <t>86457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108370</t>
+          <t>108438</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137659</t>
+          <t>138559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>178093</t>
+          <t>178774</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>216109</t>
+          <t>217866</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>200413</t>
+          <t>200191</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229072</t>
+          <t>229267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176644</t>
+          <t>177870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>208398</t>
+          <t>210401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>386036</t>
+          <t>384156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>428973</t>
+          <t>429786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>17776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27448</t>
+          <t>26748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23310</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>40047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18722</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35444</t>
+          <t>34609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34541</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14378</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>28192</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>36558</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57134</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77932</t>
+          <t>78568</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97656</t>
+          <t>97014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70453</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87647</t>
+          <t>86916</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>153707</t>
+          <t>154135</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179457</t>
+          <t>179354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16773</t>
+          <t>17606</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>28989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47581</t>
+          <t>47347</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>71906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82773</t>
+          <t>81982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114281</t>
+          <t>111985</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>45556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70187</t>
+          <t>68816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63978</t>
+          <t>63107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>95471</t>
+          <t>93858</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>129163</t>
+          <t>126870</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>96390</t>
+          <t>95845</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>125929</t>
+          <t>126992</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>145018</t>
+          <t>145617</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>181033</t>
+          <t>179194</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>248952</t>
+          <t>249523</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>293530</t>
+          <t>296990</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>336336</t>
+          <t>337753</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>373170</t>
+          <t>374853</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>284688</t>
+          <t>286140</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>323452</t>
+          <t>326805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>630973</t>
+          <t>631960</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>686263</t>
+          <t>689398</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>27420</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35856</t>
+          <t>35497</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>57309</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13015</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21179</t>
+          <t>21787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25168</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>20965</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25865</t>
+          <t>25437</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41672</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>26307</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39262</t>
+          <t>39552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38808</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56257</t>
+          <t>55664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74352</t>
+          <t>74641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34429</t>
+          <t>34666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>40163</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62496</t>
+          <t>62547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63495</t>
+          <t>65689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91184</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37114</t>
+          <t>36605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>58618</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40564</t>
+          <t>40289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62288</t>
+          <t>61514</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83848</t>
+          <t>83521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114187</t>
+          <t>114729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59906</t>
+          <t>58402</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84418</t>
+          <t>83563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72492</t>
+          <t>72913</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>99758</t>
+          <t>99376</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,47 +4650,47 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>20,1%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>27,4%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>157635</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>139917</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>175604</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>22,51%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>19,98%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>27,5%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>157635</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>139763</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>176461</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165496</t>
+          <t>164357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193865</t>
+          <t>194452</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146898</t>
+          <t>147437</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178403</t>
+          <t>178877</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>319722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>363480</t>
+          <t>363092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21019</t>
+          <t>21679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37044</t>
+          <t>37309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>18692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29211</t>
+          <t>29291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19116</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>17608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32904</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21020</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36547</t>
+          <t>37307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>31103</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>48600</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57912</t>
+          <t>56499</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81373</t>
+          <t>79079</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62770</t>
+          <t>62803</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81072</t>
+          <t>81080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51373</t>
+          <t>51837</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71002</t>
+          <t>69996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120292</t>
+          <t>120249</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146301</t>
+          <t>145315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,47%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28631</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>48738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58476</t>
+          <t>57710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86049</t>
+          <t>83765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92391</t>
+          <t>92975</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125815</t>
+          <t>126755</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54134</t>
+          <t>53881</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78281</t>
+          <t>78965</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57708</t>
+          <t>57485</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>84247</t>
+          <t>83080</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119332</t>
+          <t>119632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>155755</t>
+          <t>156642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103521</t>
+          <t>105510</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134384</t>
+          <t>135681</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>122788</t>
+          <t>123476</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156225</t>
+          <t>157455</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>235850</t>
+          <t>233994</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>281448</t>
+          <t>280380</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>266822</t>
+          <t>264766</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>305314</t>
+          <t>303521</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>235405</t>
+          <t>234871</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275027</t>
+          <t>274406</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>514744</t>
+          <t>510267</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>567662</t>
+          <t>568259</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28748</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26435</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31108</t>
+          <t>30524</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17786</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>19128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20649</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>22105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23794</t>
+          <t>23731</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>39661</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>23977</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>17466</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29815</t>
+          <t>29454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34914</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50230</t>
+          <t>50613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19736</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29791</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>48905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63841</t>
+          <t>63657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>27646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46170</t>
+          <t>46318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39960</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61459</t>
+          <t>59872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72141</t>
+          <t>70961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99620</t>
+          <t>99940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65915</t>
+          <t>64285</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89779</t>
+          <t>89985</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71173</t>
+          <t>73660</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98700</t>
+          <t>99800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>143808</t>
+          <t>145123</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>179959</t>
+          <t>181398</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211238</t>
+          <t>210162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242982</t>
+          <t>241486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176620</t>
+          <t>177275</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211447</t>
+          <t>209541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>398070</t>
+          <t>398082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>442211</t>
+          <t>442335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,83%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25480</t>
+          <t>26378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>19713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36795</t>
+          <t>37342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35021</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56344</t>
+          <t>55627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14815</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>23801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18810</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34649</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30658</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>47428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43176</t>
+          <t>43015</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65180</t>
+          <t>63339</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75743</t>
+          <t>74405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92878</t>
+          <t>92228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,49 +8369,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>58,76%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>71553</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>62644</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>81325</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>52,64%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>46,08%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>59,82%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>73,35%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>71553</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>61590</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>81046</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>45,31%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>59,62%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>227</t>
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142383</t>
+          <t>143169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169815</t>
+          <t>167741</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>63,89%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10910</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16806</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>37075</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40515</t>
+          <t>40101</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>63514</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67191</t>
+          <t>65675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94749</t>
+          <t>95879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>44290</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68207</t>
+          <t>67678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57885</t>
+          <t>57545</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83760</t>
+          <t>83776</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>107131</t>
+          <t>106281</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>142754</t>
+          <t>141009</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92716</t>
+          <t>91196</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121706</t>
+          <t>122103</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>121423</t>
+          <t>124718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>157620</t>
+          <t>159599</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>225360</t>
+          <t>223298</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>271412</t>
+          <t>269011</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>310857</t>
+          <t>311662</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>347698</t>
+          <t>349488</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>269854</t>
+          <t>270464</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>309996</t>
+          <t>308918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>590482</t>
+          <t>592724</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>645371</t>
+          <t>646396</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,29%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33272</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43492</t>
+          <t>45229</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47083</t>
+          <t>47705</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71861</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>734</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23259</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32737</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>21181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35262</t>
+          <t>34794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39951</t>
+          <t>39091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60940</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>62,48%</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>23516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>29894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37119</t>
+          <t>37140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35576</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61347</t>
+          <t>60874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36243</t>
+          <t>37237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47182</t>
+          <t>45722</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79031</t>
+          <t>77310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70949</t>
+          <t>70473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>105373</t>
+          <t>108336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50910</t>
+          <t>51140</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81067</t>
+          <t>79597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84440</t>
+          <t>85734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124831</t>
+          <t>126383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144001</t>
+          <t>143471</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197546</t>
+          <t>194801</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>235933</t>
+          <t>235153</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>286637</t>
+          <t>283002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>214369</t>
+          <t>214117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>262516</t>
+          <t>258487</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>457552</t>
+          <t>458385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>531363</t>
+          <t>532797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,03%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18705</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35701</t>
+          <t>35472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>40525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66925</t>
+          <t>65954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25706</t>
+          <t>26552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26148</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>21881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40594</t>
+          <t>40824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>38739</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61590</t>
+          <t>61128</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81364</t>
+          <t>81664</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99173</t>
+          <t>98748</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>81649</t>
+          <t>81824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103760</t>
+          <t>102990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>168368</t>
+          <t>168060</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>196272</t>
+          <t>195482</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,25%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>16675</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32537</t>
+          <t>31322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37105</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47787</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49102</t>
+          <t>48906</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76193</t>
+          <t>76794</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29404</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49146</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58401</t>
+          <t>59487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92485</t>
+          <t>93889</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>95507</t>
+          <t>94848</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>136068</t>
+          <t>136892</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79438</t>
+          <t>79482</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116357</t>
+          <t>116070</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>122706</t>
+          <t>122122</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>166564</t>
+          <t>167659</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>211601</t>
+          <t>213727</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>270378</t>
+          <t>271226</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>341245</t>
+          <t>343428</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>396999</t>
+          <t>396177</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>329371</t>
+          <t>330449</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>384852</t>
+          <t>384480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>688123</t>
+          <t>688805</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>764680</t>
+          <t>762949</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34666</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66474</t>
+          <t>65402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>52633</t>
+          <t>54215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70802</t>
+          <t>69830</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>110023</t>
+          <t>107145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_inf_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_R-Estudios-trans_orig.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>192941</v>
+        <v>193591</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>176667</v>
+        <v>177118</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>208333</v>
+        <v>209264</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4705493174702334</v>
+        <v>0.4721347475673388</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4308587219588033</v>
+        <v>0.431959565143186</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5080882344138394</v>
+        <v>0.5103580022965728</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>320</v>
@@ -1415,25 +1415,25 @@
         <v>0.648892657013878</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>407646</v>
+        <v>408296</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>388206</v>
+        <v>388195</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>428855</v>
+        <v>428914</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.5348757095455606</v>
+        <v>0.5357286858120685</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.5093684991309724</v>
+        <v>0.5093542669191322</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5627042909590457</v>
+        <v>0.5627818546876258</v>
       </c>
     </row>
     <row r="14">
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>18903</v>
+        <v>18253</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>12606</v>
+        <v>12160</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>26479</v>
+        <v>26120</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.04610145684670065</v>
+        <v>0.04451602674959529</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.03074479811281753</v>
+        <v>0.02965570451839107</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.06457770649285156</v>
+        <v>0.06370237998092501</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>18</v>
@@ -1486,25 +1486,25 @@
         <v>0.05149257487662402</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>30541</v>
+        <v>29891</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>22949</v>
+        <v>22290</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>40444</v>
+        <v>39714</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.04007357394970821</v>
+        <v>0.03922059768320034</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.03011208952730432</v>
+        <v>0.02924660374067671</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.0530665584433747</v>
+        <v>0.05210946226937681</v>
       </c>
     </row>
     <row r="15">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2233,25 +2233,25 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>304213</v>
+        <v>304863</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>285570</v>
+        <v>286131</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>324293</v>
+        <v>324710</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5024551392778183</v>
+        <v>0.5035288487457855</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.4716626792796453</v>
+        <v>0.4725897824735413</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5356197657406884</v>
+        <v>0.5363088091232465</v>
       </c>
       <c r="J25" s="5" t="n">
         <v>525</v>
@@ -2275,25 +2275,25 @@
         <v>0.6454744660949693</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>659528</v>
+        <v>660178</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>633140</v>
+        <v>633820</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>687943</v>
+        <v>688456</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.5572576635126306</v>
+        <v>0.5578069385938749</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.5349609214065915</v>
+        <v>0.5355359463257564</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.5812662489721956</v>
+        <v>0.5816993726167565</v>
       </c>
     </row>
     <row r="26">
@@ -2304,25 +2304,25 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>26250</v>
+        <v>25599</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>19267</v>
+        <v>18573</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>34699</v>
+        <v>34180</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.04335525635786645</v>
+        <v>0.04228154688989916</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.03182265127449958</v>
+        <v>0.03067645825931641</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.05731068622694988</v>
+        <v>0.0564528716715501</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>29</v>
@@ -2346,25 +2346,25 @@
         <v>0.0458607535520415</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R26" s="5" t="n">
-        <v>45282</v>
+        <v>44632</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>36104</v>
+        <v>35378</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>57176</v>
+        <v>56272</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.03826000231423884</v>
+        <v>0.03771072723299453</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.03050524197936881</v>
+        <v>0.02989174778838683</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.04830994509272634</v>
+        <v>0.04754635947722598</v>
       </c>
     </row>
     <row r="27">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Obesidad intensa</t>
+          <t>Obsesidad intesa</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
